--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_53_R6.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_53_R6.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.731</v>
+        <v>6.4415</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4451</v>
+        <v>8.886699999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.7141</v>
+        <v>-2.4452</v>
       </c>
       <c r="G2" t="n">
         <v>1.9913</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3117</v>
+        <v>1.0222</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5613</v>
+        <v>1.0029</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2495</v>
+        <v>0.0193</v>
       </c>
       <c r="V2" t="n">
         <v>2.9641</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1685</v>
+        <v>2.3584</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1871</v>
+        <v>1.7467</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.6117</v>
       </c>
       <c r="G3" t="n">
         <v>1.7837</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5266</v>
+        <v>0.7165</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9911</v>
+        <v>0.5507</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5355</v>
+        <v>0.1658</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5511</v>
+        <v>1.6269</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4747</v>
+        <v>1.4498</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0764</v>
+        <v>0.1772</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9726</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6207</v>
+        <v>0.4551</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4244</v>
+        <v>0.5507</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1964</v>
+        <v>-0.0955</v>
       </c>
       <c r="V4" t="n">
         <v>2.1444</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. SESTINA</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0057</v>
+        <v>0.4398</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4637</v>
+        <v>3.0846</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4694</v>
+        <v>-2.6448</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.8696</v>
+        <v>0.6653</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8307</v>
+        <v>2.0838</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.7003</v>
+        <v>-1.4186</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.5294</v>
+        <v>4.4784</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2183</v>
+        <v>3.3141</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.7477</v>
+        <v>1.1643</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3401</v>
+        <v>-3.8131</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3875</v>
+        <v>-1.2303</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0474</v>
+        <v>-2.5829</v>
       </c>
       <c r="P5" t="n">
         <v>1.3917</v>
@@ -844,28 +844,28 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1615</v>
+        <v>-0.8285</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0657</v>
+        <v>-0.6051</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0958</v>
+        <v>-0.2234</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.7886</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>N. SESTINA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3927</v>
+        <v>-0.1315</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4202</v>
+        <v>-0.6682</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8128</v>
+        <v>0.5367</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6653</v>
+        <v>-1.8696</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0838</v>
+        <v>0.8307</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4186</v>
+        <v>-2.7003</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4784</v>
+        <v>-1.5294</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3141</v>
+        <v>2.2183</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1643</v>
+        <v>-3.7477</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.8131</v>
+        <v>-0.3401</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2303</v>
+        <v>-1.3875</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.5829</v>
+        <v>1.0474</v>
       </c>
       <c r="P6" t="n">
         <v>1.3917</v>
@@ -922,22 +922,22 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.661</v>
+        <v>1.0242</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2696</v>
+        <v>0.8612</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3914</v>
+        <v>0.163</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7886</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6451</v>
+        <v>-0.2502</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2111</v>
+        <v>0.2175</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.434</v>
+        <v>-0.4676</v>
       </c>
       <c r="G7" t="n">
         <v>0.0682</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3369</v>
+        <v>0.058</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3655</v>
+        <v>0.063</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0286</v>
+        <v>-0.005</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.731</v>
+        <v>-0.9588</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2923</v>
+        <v>1.367</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0233</v>
+        <v>-2.3258</v>
       </c>
       <c r="G8" t="n">
         <v>-3.6708</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1718</v>
+        <v>-0.056</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.326</v>
+        <v>-0.2513</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4977</v>
+        <v>0.1953</v>
       </c>
       <c r="V8" t="n">
         <v>1.6083</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1469</v>
+        <v>-1.2005</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0547</v>
+        <v>3.7323</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.2016</v>
+        <v>-4.9328</v>
       </c>
       <c r="G9" t="n">
         <v>0.09080000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0211</v>
+        <v>-0.0747</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8338</v>
+        <v>0.5113</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8549</v>
+        <v>-0.586</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1444</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7519</v>
+        <v>-3.3234</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6395</v>
+        <v>-1.2109</v>
       </c>
       <c r="F10" t="n">
         <v>-2.1124</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.224</v>
+        <v>0.2045</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0668</v>
+        <v>0.3618</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1573</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.0413</v>
+        <v>-8.134600000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7856</v>
+        <v>-1.7109</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.2556</v>
+        <v>-6.4237</v>
       </c>
       <c r="G11" t="n">
         <v>-6.7077</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0294</v>
+        <v>-0.1228</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.326</v>
+        <v>-0.2513</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2965</v>
+        <v>0.1285</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.252599999999999</v>
+        <v>-3.132400000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>15.7742</v>
+        <v>16.8946</v>
       </c>
       <c r="F12" t="n">
-        <v>-20.0266</v>
+        <v>-20.0267</v>
       </c>
       <c r="G12" t="n">
         <v>-11.0771</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5707999999999996</v>
+        <v>-0.5708000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-10.5064</v>
@@ -1390,22 +1390,22 @@
         <v>10.438</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2785</v>
+        <v>2.3985</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6736</v>
+        <v>2.7939</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3954</v>
+        <v>-0.3952999999999998</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2524999999999999</v>
+        <v>-0.2524999999999995</v>
       </c>
       <c r="W12" t="n">
         <v>7.425800000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.678299999999999</v>
+        <v>-7.678300000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4628</v>
+        <v>3.9182</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4345</v>
+        <v>4.5525</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9717</v>
+        <v>-0.6343</v>
       </c>
       <c r="G13" t="n">
         <v>1.8802</v>
@@ -1468,13 +1468,13 @@
         <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2759</v>
+        <v>0.7312</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2794</v>
+        <v>0.3973</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0035</v>
+        <v>0.3339</v>
       </c>
       <c r="V13" t="n">
         <v>2.0026</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4612</v>
+        <v>3.2589</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6834</v>
+        <v>2.4475</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7778</v>
+        <v>0.8115</v>
       </c>
       <c r="G14" t="n">
         <v>2.8772</v>
@@ -1546,13 +1546,13 @@
         <v>0.232</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6357</v>
+        <v>0.4334</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2636</v>
+        <v>0.0277</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3721</v>
+        <v>0.4057</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2836</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0921</v>
+        <v>2.6926</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6276</v>
+        <v>5.7456</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5355</v>
+        <v>-3.053</v>
       </c>
       <c r="G15" t="n">
         <v>2.2633</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2614</v>
+        <v>0.3391</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0474</v>
+        <v>0.1654</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3088</v>
+        <v>0.1737</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0031</v>
+        <v>1.6277</v>
       </c>
       <c r="E16" t="n">
-        <v>4.24</v>
+        <v>3.8861</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2369</v>
+        <v>-2.2584</v>
       </c>
       <c r="G16" t="n">
         <v>3.7156</v>
@@ -1702,13 +1702,13 @@
         <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3418</v>
+        <v>-0.0336</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4208</v>
+        <v>0.067</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0791</v>
+        <v>-0.1006</v>
       </c>
       <c r="V16" t="n">
         <v>-2.2862</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7679</v>
+        <v>1.187</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3561</v>
+        <v>3.6662</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4118</v>
+        <v>-2.4792</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5134</v>
+        <v>2.6758</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3193</v>
+        <v>2.0467</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1941</v>
+        <v>0.6291</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3561</v>
+        <v>4.4989</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3193</v>
+        <v>3.445</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0368</v>
+        <v>1.0539</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1573</v>
+        <v>-1.8231</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.3983</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1573</v>
+        <v>-0.4248</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3062</v>
+        <v>0.2998</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.0435</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3062</v>
+        <v>0.2563</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2836</v>
+        <v>-1.3247</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2836</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6072</v>
+        <v>1.1018</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7437</v>
+        <v>2.2155</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1365</v>
+        <v>-1.1137</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6509</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4946</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7389</v>
+        <v>-0.2671</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2443</v>
+        <v>0.2671</v>
       </c>
       <c r="V18" t="n">
         <v>3.2166</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3036</v>
+        <v>0.6796</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9869</v>
+        <v>-0.869</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2905</v>
+        <v>1.5486</v>
       </c>
       <c r="G19" t="n">
         <v>3.0435</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6524</v>
+        <v>-0.2763</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4283</v>
+        <v>-0.1702</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.154</v>
+        <v>0.6671</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9585</v>
+        <v>0.3561</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8045</v>
+        <v>0.311</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6758</v>
+        <v>0.5134</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0467</v>
+        <v>0.3193</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6291</v>
+        <v>0.1941</v>
       </c>
       <c r="J20" t="n">
-        <v>4.4989</v>
+        <v>0.3561</v>
       </c>
       <c r="K20" t="n">
-        <v>3.445</v>
+        <v>0.3193</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0539</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8231</v>
+        <v>0.1573</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3983</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4248</v>
+        <v>0.1573</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7332</v>
+        <v>0.2054</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.2054</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3247</v>
+        <v>-0.2836</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.012</v>
+        <v>-0.2992</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4589</v>
+        <v>-0.1051</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5531</v>
+        <v>-0.1942</v>
       </c>
       <c r="G21" t="n">
         <v>0.8023</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3478</v>
+        <v>-0.635</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8136</v>
+        <v>-0.4597</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5342</v>
+        <v>-0.1753</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9304</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0533</v>
+        <v>-2.2714</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1404</v>
+        <v>-2.0224</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0871</v>
+        <v>-0.249</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4163</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0589</v>
+        <v>-0.1592</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3655</v>
+        <v>-0.2475</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4244</v>
+        <v>0.0883</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.399</v>
+        <v>-2.6025</v>
       </c>
       <c r="E23" t="n">
-        <v>2.4363</v>
+        <v>-0.9851</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.8353</v>
+        <v>-1.6174</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4374</v>
+        <v>-0.1895</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.1162</v>
+        <v>1.3698</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3212</v>
+        <v>-1.5592</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3086</v>
+        <v>1.1938</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.371</v>
+        <v>2.1174</v>
       </c>
       <c r="L23" t="n">
-        <v>1.6796</v>
+        <v>-0.9236</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.746</v>
+        <v>-1.3833</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7452</v>
+        <v>-0.7477</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0008</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6959</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1312</v>
+        <v>-0.0059</v>
       </c>
       <c r="T23" t="n">
-        <v>1.8442</v>
+        <v>0.2282</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.713</v>
+        <v>-0.2341</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1351</v>
+        <v>-3.3483</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8671</v>
+        <v>1.1388</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.268</v>
+        <v>-4.4871</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1895</v>
+        <v>-3.4374</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3698</v>
+        <v>-3.1162</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5592</v>
+        <v>-0.3212</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1938</v>
+        <v>0.3086</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1174</v>
+        <v>-1.371</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.9236</v>
+        <v>1.6796</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3833</v>
+        <v>-3.746</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7477</v>
+        <v>-1.7452</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-2.0008</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4793</v>
+        <v>0.6959</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5386</v>
+        <v>0.1819</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3462</v>
+        <v>0.5467</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8847</v>
+        <v>-0.3648</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0722</v>
+        <v>0.2836</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.2525</v>
+        <v>6.611499999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>20.0268</v>
+        <v>20.0267</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.7743</v>
+        <v>-13.4152</v>
       </c>
       <c r="G25" t="n">
         <v>11.0772</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5708</v>
+        <v>0.5708000000000002</v>
       </c>
       <c r="I25" t="n">
         <v>10.5064</v>
@@ -2389,7 +2389,7 @@
         <v>-11.314</v>
       </c>
       <c r="N25" t="n">
-        <v>-9.157300000000001</v>
+        <v>-9.157299999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-2.1567</v>
@@ -2404,16 +2404,16 @@
         <v>4.639399999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2783</v>
+        <v>1.0808</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3954000000000001</v>
+        <v>0.3954</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6736</v>
+        <v>0.6854</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2525000000000005</v>
+        <v>0.2525000000000002</v>
       </c>
       <c r="W25" t="n">
         <v>7.6783</v>
